--- a/artfynd/A 4256-2022 artfynd.xlsx
+++ b/artfynd/A 4256-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,121 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134015669</v>
+      </c>
+      <c r="B4" t="n">
+        <v>44545</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>215210</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Asksolvecklare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pammene suspectana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Lienig &amp; Zeller, 1846)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>pheromone</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Håckla äng, Vreta Kloster kyrka, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>528403</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6481108</v>
+      </c>
+      <c r="S4" t="n">
+        <v>77</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Göran Friman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Göran Friman, Bert Östholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4256-2022 artfynd.xlsx
+++ b/artfynd/A 4256-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133998945</v>
       </c>
       <c r="B2" t="n">
-        <v>58358</v>
+        <v>58365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133988966</v>
       </c>
       <c r="B3" t="n">
-        <v>58681</v>
+        <v>58688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>134015669</v>
       </c>
       <c r="B4" t="n">
-        <v>44545</v>
+        <v>44550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4256-2022 artfynd.xlsx
+++ b/artfynd/A 4256-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133998945</v>
       </c>
       <c r="B2" t="n">
-        <v>58365</v>
+        <v>58375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133988966</v>
       </c>
       <c r="B3" t="n">
-        <v>58688</v>
+        <v>58698</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4256-2022 artfynd.xlsx
+++ b/artfynd/A 4256-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133998945</v>
+        <v>133988963</v>
       </c>
       <c r="B2" t="n">
-        <v>58375</v>
+        <v>58231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>102980</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,27 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133988966</v>
+        <v>133998945</v>
       </c>
       <c r="B3" t="n">
-        <v>58698</v>
+        <v>58375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,18 +824,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -880,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134015669</v>
+        <v>133988966</v>
       </c>
       <c r="B4" t="n">
-        <v>44550</v>
+        <v>58698</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>215210</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asksolvecklare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pammene suspectana</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lienig &amp; Zeller, 1846)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,19 +946,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>pheromone</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Håckla äng, Vreta Kloster kyrka, Ög</t>
@@ -999,12 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1018,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,10 +1029,125 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Göran Friman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134015669</v>
+      </c>
+      <c r="B5" t="n">
+        <v>44550</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>215210</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Asksolvecklare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pammene suspectana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Lienig &amp; Zeller, 1846)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>pheromone</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Håckla äng, Vreta Kloster kyrka, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528403</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6481108</v>
+      </c>
+      <c r="S5" t="n">
+        <v>77</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Friman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Göran Friman, Bert Östholm</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4256-2022 artfynd.xlsx
+++ b/artfynd/A 4256-2022 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Molin, Sigrid Gustafsson, Julia Svensson</t>
+          <t>Julia Svensson, Sigrid Gustafsson, Johan Molin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 4256-2022 artfynd.xlsx
+++ b/artfynd/A 4256-2022 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julia Svensson, Sigrid Gustafsson, Johan Molin</t>
+          <t>Johan Molin, Sigrid Gustafsson, Julia Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 4256-2022 artfynd.xlsx
+++ b/artfynd/A 4256-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134807862</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133988963</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133998945</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133988966</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,8 +1288,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134015669</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>